--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
+        <v>92690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92690</v>
+        <v>92691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92691</v>
+        <v>92697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92697</v>
+        <v>92701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92703</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92718</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92721</v>
+        <v>92731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92732</v>
+        <v>92735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92737</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92755</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31609-2026 artfynd.xlsx
+++ b/artfynd/A 31609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008062</v>
       </c>
       <c r="B2" t="n">
-        <v>92759</v>
+        <v>92762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137008061</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
